--- a/data/reference/digital_asset_research_universe.xlsx
+++ b/data/reference/digital_asset_research_universe.xlsx
@@ -144,10 +144,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -156,16 +156,16 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -639,24 +639,24 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  verified</t>
+          <t xml:space="preserve">  reviewed</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>60 — evidence plus independent blind review</t>
+          <t>10 — sourced AND independently blind-reviewed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  drafted</t>
+          <t xml:space="preserve">  sourced</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>59 — sourced, awaiting blind review</t>
+          <t>109 — dated primary source, NOT independently reviewed</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Green verified · amber drafted · red pending · grey provisional. A pending cell never defaults to zero.</t>
+          <t>Green reviewed · amber sourced but not reviewed · red pending · grey provisional. Only green supports a reliability claim.</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>codes_verified</t>
+          <t>codes_reviewed</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>codes_drafted</t>
+          <t>codes_sourced</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -910,15 +910,15 @@
           <t>Large, liquid market representative</t>
         </is>
       </c>
-      <c r="K5" s="7" t="n">
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="7" t="n"/>
       <c r="M5" s="7" t="n"/>
       <c r="N5" s="7" t="n"/>
       <c r="O5" s="10" t="inlineStr">
         <is>
-          <t>complete verified</t>
+          <t>fully evidenced</t>
         </is>
       </c>
     </row>
@@ -966,15 +966,15 @@
           <t>Large, liquid market representative</t>
         </is>
       </c>
-      <c r="K6" s="7" t="n">
+      <c r="K6" s="7" t="n"/>
+      <c r="L6" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="L6" s="7" t="n"/>
       <c r="M6" s="7" t="n"/>
       <c r="N6" s="7" t="n"/>
       <c r="O6" s="10" t="inlineStr">
         <is>
-          <t>complete verified</t>
+          <t>fully evidenced</t>
         </is>
       </c>
     </row>
@@ -1022,15 +1022,15 @@
           <t>Large, liquid market representative</t>
         </is>
       </c>
-      <c r="K7" s="7" t="n">
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="L7" s="7" t="n"/>
       <c r="M7" s="7" t="n"/>
       <c r="N7" s="7" t="n"/>
       <c r="O7" s="10" t="inlineStr">
         <is>
-          <t>complete verified</t>
+          <t>fully evidenced</t>
         </is>
       </c>
     </row>
@@ -1078,9 +1078,11 @@
           <t>Large, liquid market representative</t>
         </is>
       </c>
-      <c r="K8" s="7" t="n"/>
+      <c r="K8" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="L8" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M8" s="7" t="n"/>
       <c r="N8" s="7" t="n">
@@ -1088,7 +1090,7 @@
       </c>
       <c r="O8" s="11" t="inlineStr">
         <is>
-          <t>in tranche review</t>
+          <t>in tranche</t>
         </is>
       </c>
     </row>
@@ -1136,9 +1138,11 @@
           <t>Large, liquid market representative</t>
         </is>
       </c>
-      <c r="K9" s="7" t="n"/>
+      <c r="K9" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="L9" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M9" s="7" t="n"/>
       <c r="N9" s="7" t="n">
@@ -1146,7 +1150,7 @@
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>in tranche review</t>
+          <t>in tranche</t>
         </is>
       </c>
     </row>
@@ -1194,9 +1198,11 @@
           <t>Large, liquid market representative</t>
         </is>
       </c>
-      <c r="K10" s="7" t="n"/>
+      <c r="K10" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="L10" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M10" s="7" t="n"/>
       <c r="N10" s="7" t="n">
@@ -1204,7 +1210,7 @@
       </c>
       <c r="O10" s="11" t="inlineStr">
         <is>
-          <t>in tranche review</t>
+          <t>in tranche</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1326,7 @@
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>in tranche review</t>
+          <t>in tranche</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1386,7 @@
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>in tranche review</t>
+          <t>in tranche</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1446,7 @@
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>in tranche review</t>
+          <t>in tranche</t>
         </is>
       </c>
     </row>
@@ -1488,9 +1494,11 @@
           <t>Large, liquid market representative</t>
         </is>
       </c>
-      <c r="K15" s="7" t="n"/>
+      <c r="K15" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="L15" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n">
@@ -1498,7 +1506,7 @@
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>in tranche review</t>
+          <t>in tranche</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1620,7 @@
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>in tranche review</t>
+          <t>in tranche</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1680,7 @@
       </c>
       <c r="O18" s="11" t="inlineStr">
         <is>
-          <t>in tranche review</t>
+          <t>in tranche</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1740,7 @@
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>in tranche review</t>
+          <t>in tranche</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1800,7 @@
       </c>
       <c r="O20" s="11" t="inlineStr">
         <is>
-          <t>in tranche review</t>
+          <t>in tranche</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1858,7 @@
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>in tranche review</t>
+          <t>in tranche</t>
         </is>
       </c>
     </row>
@@ -1898,9 +1906,11 @@
           <t>Adds valuation-mechanism or sector coverage</t>
         </is>
       </c>
-      <c r="K22" s="7" t="n"/>
+      <c r="K22" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="L22" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M22" s="7" t="n"/>
       <c r="N22" s="7" t="n">
@@ -1908,7 +1918,7 @@
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>in tranche review</t>
+          <t>in tranche</t>
         </is>
       </c>
     </row>
@@ -2058,15 +2068,15 @@
           <t>Adds valuation-mechanism or sector coverage</t>
         </is>
       </c>
-      <c r="K25" s="7" t="n">
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="L25" s="7" t="n"/>
       <c r="M25" s="7" t="n"/>
       <c r="N25" s="7" t="n"/>
       <c r="O25" s="10" t="inlineStr">
         <is>
-          <t>complete verified</t>
+          <t>fully evidenced</t>
         </is>
       </c>
     </row>
@@ -2114,15 +2124,15 @@
           <t>Adds valuation-mechanism or sector coverage</t>
         </is>
       </c>
-      <c r="K26" s="7" t="n">
+      <c r="K26" s="7" t="n"/>
+      <c r="L26" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="L26" s="7" t="n"/>
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="7" t="n"/>
       <c r="O26" s="10" t="inlineStr">
         <is>
-          <t>complete verified</t>
+          <t>fully evidenced</t>
         </is>
       </c>
     </row>
@@ -2170,15 +2180,15 @@
           <t>Adds valuation-mechanism or sector coverage</t>
         </is>
       </c>
-      <c r="K27" s="7" t="n">
+      <c r="K27" s="7" t="n"/>
+      <c r="L27" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="L27" s="7" t="n"/>
       <c r="M27" s="7" t="n"/>
       <c r="N27" s="7" t="n"/>
       <c r="O27" s="10" t="inlineStr">
         <is>
-          <t>complete verified</t>
+          <t>fully evidenced</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2238,7 @@
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>in tranche review</t>
+          <t>in tranche</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3317,7 @@
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>complete verified</t>
+          <t>fully evidenced</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3372,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>complete verified</t>
+          <t>fully evidenced</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3427,7 @@
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>complete verified</t>
+          <t>fully evidenced</t>
         </is>
       </c>
     </row>
@@ -3436,22 +3446,22 @@
       <c r="D8" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="20" t="n">
+      <c r="E8" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="16" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="21" t="n">
+      <c r="H8" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="20" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="19" t="n">
@@ -3460,7 +3470,7 @@
       <c r="L8" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="M8" s="21" t="n">
+      <c r="M8" s="20" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="17" t="n">
@@ -3468,7 +3478,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>provisional/drafted</t>
+          <t>mixed</t>
         </is>
       </c>
     </row>
@@ -3484,25 +3494,25 @@
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr"/>
-      <c r="D9" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="19" t="n">
+      <c r="D9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="21" t="n">
+      <c r="J9" s="20" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="19" t="n">
@@ -3511,7 +3521,7 @@
       <c r="L9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="M9" s="21" t="n">
+      <c r="M9" s="20" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="17" t="n">
@@ -3519,7 +3529,7 @@
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>provisional/drafted</t>
+          <t>mixed</t>
         </is>
       </c>
     </row>
@@ -3538,16 +3548,16 @@
       <c r="D10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="19" t="n">
+      <c r="E10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="20" t="n">
+      <c r="H10" s="16" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="18" t="n">
@@ -3570,7 +3580,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>provisional/drafted</t>
+          <t>mixed</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3596,7 @@
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr"/>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -3598,10 +3608,10 @@
       <c r="G11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="21" t="n">
+      <c r="H11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="18" t="n">
@@ -3621,7 +3631,7 @@
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>provisional/drafted</t>
+          <t>mixed</t>
         </is>
       </c>
     </row>
@@ -3640,25 +3650,25 @@
       <c r="D12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="22" t="n"/>
-      <c r="H12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="22" t="n"/>
-      <c r="L12" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="21" t="n">
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="21" t="n"/>
+      <c r="L12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="20" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="17" t="n">
@@ -3685,29 +3695,29 @@
       <c r="D13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="21" t="n">
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="20" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="17" t="n">
@@ -3731,28 +3741,28 @@
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr"/>
-      <c r="D14" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="22" t="n"/>
+      <c r="D14" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="21" t="n"/>
       <c r="L14" s="18" t="n">
         <v>1</v>
       </c>
@@ -3780,19 +3790,19 @@
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr"/>
-      <c r="D15" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="19" t="n">
+      <c r="D15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="18" t="n">
@@ -3801,13 +3811,13 @@
       <c r="J15" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="20" t="n">
+      <c r="K15" s="22" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="M15" s="21" t="n">
+      <c r="M15" s="20" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="17" t="n">
@@ -3815,7 +3825,7 @@
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>provisional/drafted</t>
+          <t>mixed</t>
         </is>
       </c>
     </row>
@@ -3837,28 +3847,28 @@
       <c r="E16" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="21" t="n">
+      <c r="F16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="20" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="17" t="n">
@@ -3866,7 +3876,7 @@
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>provisional/drafted</t>
+          <t>mixed</t>
         </is>
       </c>
     </row>
@@ -3885,31 +3895,31 @@
       <c r="D17" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="21" t="n">
+      <c r="E17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="20" t="n">
+      <c r="K17" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="M17" s="21" t="n">
+      <c r="M17" s="20" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="17" t="n">
@@ -3917,7 +3927,7 @@
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>provisional/drafted</t>
+          <t>mixed</t>
         </is>
       </c>
     </row>
@@ -3936,29 +3946,29 @@
       <c r="D18" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="22" t="n"/>
-      <c r="F18" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="21" t="n">
+      <c r="E18" s="21" t="n"/>
+      <c r="F18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="20" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="17" t="n">
@@ -3985,27 +3995,27 @@
       <c r="D19" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="21" t="n">
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="21" t="n"/>
+      <c r="H19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="20" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="17" t="n">
@@ -4029,26 +4039,26 @@
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr"/>
-      <c r="D20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="22" t="n"/>
-      <c r="H20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="21" t="n">
+      <c r="D20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="K20" s="20" t="n">
+      <c r="K20" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="18" t="n">
@@ -4078,19 +4088,19 @@
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr"/>
-      <c r="D21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="19" t="n">
+      <c r="D21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="18" t="n">
@@ -4099,7 +4109,7 @@
       <c r="J21" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="K21" s="20" t="n">
+      <c r="K21" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="18" t="n">
@@ -4113,7 +4123,7 @@
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>provisional/drafted</t>
+          <t>mixed</t>
         </is>
       </c>
     </row>
@@ -4129,19 +4139,19 @@
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr"/>
-      <c r="D22" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="19" t="n">
+      <c r="D22" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="19" t="n">
+      <c r="H22" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I22" s="18" t="n">
@@ -4164,7 +4174,7 @@
       </c>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>provisional/drafted</t>
+          <t>mixed</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4190,7 @@
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr"/>
-      <c r="D23" s="21" t="n">
+      <c r="D23" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="18" t="n">
@@ -4189,10 +4199,10 @@
       <c r="F23" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="21" t="n">
+      <c r="G23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="18" t="n">
@@ -4215,7 +4225,7 @@
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>provisional/drafted</t>
+          <t>mixed</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4241,7 @@
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr"/>
-      <c r="D24" s="21" t="n">
+      <c r="D24" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="18" t="n">
@@ -4240,13 +4250,13 @@
       <c r="F24" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="21" t="n">
+      <c r="G24" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="21" t="n">
+      <c r="I24" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="18" t="n">
@@ -4266,7 +4276,7 @@
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>provisional/drafted</t>
+          <t>mixed</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4331,7 @@
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>complete verified</t>
+          <t>fully evidenced</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4386,7 @@
       </c>
       <c r="O26" s="7" t="inlineStr">
         <is>
-          <t>complete verified</t>
+          <t>fully evidenced</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4441,7 @@
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>complete verified</t>
+          <t>fully evidenced</t>
         </is>
       </c>
     </row>
@@ -4447,27 +4457,27 @@
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr"/>
-      <c r="D28" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="22" t="n"/>
-      <c r="H28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="21" t="n">
+      <c r="D28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="21" t="n"/>
+      <c r="H28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="K28" s="22" t="n"/>
-      <c r="L28" s="21" t="n">
+      <c r="K28" s="21" t="n"/>
+      <c r="L28" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M28" s="18" t="n">
@@ -4494,7 +4504,7 @@
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr"/>
-      <c r="D29" s="21" t="n">
+      <c r="D29" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="18" t="n">
@@ -4503,13 +4513,13 @@
       <c r="F29" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="21" t="n">
+      <c r="G29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="18" t="n">
@@ -4529,7 +4539,7 @@
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>provisional/drafted</t>
+          <t>mixed</t>
         </is>
       </c>
     </row>
@@ -4543,24 +4553,24 @@
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Evidence plus independent blind review complete</t>
+          <t>Sourced AND independently blind-reviewed. Only this state supports a reliability claim.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>drafted</t>
+          <t>sourced</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Sourced by the coder, awaiting blind review</t>
+          <t>Dated primary source, audited — but NOT independently reviewed</t>
         </is>
       </c>
     </row>

--- a/data/reference/digital_asset_research_universe.xlsx
+++ b/data/reference/digital_asset_research_universe.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>109 — dated primary source, NOT independently reviewed</t>
+          <t>114 — dated primary source, NOT independently reviewed</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>11 — held for adjudication</t>
+          <t>6 — held for adjudication</t>
         </is>
       </c>
     </row>
@@ -1316,10 +1316,10 @@
       </c>
       <c r="K12" s="7" t="n"/>
       <c r="L12" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N12" s="7" t="n">
         <v>5</v>
@@ -1730,10 +1730,10 @@
       </c>
       <c r="K19" s="7" t="n"/>
       <c r="L19" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19" s="7" t="n">
         <v>5</v>
@@ -1790,11 +1790,9 @@
       </c>
       <c r="K20" s="7" t="n"/>
       <c r="L20" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M20" s="7" t="n">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M20" s="7" t="n"/>
       <c r="N20" s="7" t="n">
         <v>5</v>
       </c>
@@ -2228,10 +2226,10 @@
       <c r="J28" s="7" t="n"/>
       <c r="K28" s="7" t="n"/>
       <c r="L28" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N28" s="7" t="n">
         <v>5</v>
@@ -3654,7 +3652,9 @@
       <c r="F12" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="21" t="n"/>
+      <c r="G12" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H12" s="16" t="n">
         <v>0</v>
       </c>
@@ -3664,7 +3664,9 @@
       <c r="J12" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="21" t="n"/>
+      <c r="K12" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="20" t="n">
         <v>0</v>
       </c>
@@ -3676,7 +3678,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>3 pending</t>
+          <t>1 pending</t>
         </is>
       </c>
     </row>
@@ -3999,7 +4001,9 @@
       <c r="F19" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="21" t="n"/>
+      <c r="G19" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H19" s="15" t="n">
         <v>1</v>
       </c>
@@ -4023,7 +4027,7 @@
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>2 pending</t>
+          <t>1 pending</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4052,9 @@
       <c r="F20" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="21" t="n"/>
+      <c r="G20" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H20" s="15" t="n">
         <v>1</v>
       </c>
@@ -4072,7 +4078,7 @@
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>1 pending</t>
+          <t>mixed</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4472,9 @@
       <c r="F28" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="21" t="n"/>
+      <c r="G28" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H28" s="16" t="n">
         <v>0</v>
       </c>
@@ -4488,7 +4496,7 @@
       </c>
       <c r="O28" s="7" t="inlineStr">
         <is>
-          <t>2 pending</t>
+          <t>1 pending</t>
         </is>
       </c>
     </row>
@@ -6865,10 +6873,12 @@
           <t>VA_BURN</t>
         </is>
       </c>
-      <c r="C64" s="30" t="n"/>
+      <c r="C64" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="D64" s="30" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
@@ -6878,7 +6888,7 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>https://dogecoin.com/dogepedia/faq/putting-a-cap-on-dogecoin/</t>
+          <t>https://dogecoin.com/dogepedia/articles/what-is-a-miner/</t>
         </is>
       </c>
     </row>
@@ -6921,10 +6931,12 @@
           <t>VA_PROTOCOL</t>
         </is>
       </c>
-      <c r="C66" s="30" t="n"/>
+      <c r="C66" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="D66" s="30" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E66" s="30" t="inlineStr">
@@ -6934,7 +6946,7 @@
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>https://dogecoin.com/dogepedia/faq/putting-a-cap-on-dogecoin/</t>
+          <t>https://dogecoin.com/dogepedia/articles/what-is-a-miner/</t>
         </is>
       </c>
     </row>
@@ -7309,10 +7321,12 @@
           <t>VA_BURN</t>
         </is>
       </c>
-      <c r="C79" s="30" t="n"/>
+      <c r="C79" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="D79" s="30" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E79" s="30" t="inlineStr">
@@ -7322,7 +7336,7 @@
       </c>
       <c r="F79" s="30" t="inlineStr">
         <is>
-          <t>https://docs.hedera.com/hedera/networks/mainnet/fees</t>
+          <t>https://hedera.com/terms/</t>
         </is>
       </c>
     </row>
@@ -7605,10 +7619,12 @@
           <t>VA_BURN</t>
         </is>
       </c>
-      <c r="C89" s="30" t="n"/>
+      <c r="C89" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="D89" s="30" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E89" s="30" t="inlineStr">
@@ -7751,10 +7767,12 @@
           <t>VA_BURN</t>
         </is>
       </c>
-      <c r="C94" s="30" t="n"/>
+      <c r="C94" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="D94" s="30" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E94" s="30" t="inlineStr">
@@ -7764,7 +7782,7 @@
       </c>
       <c r="F94" s="30" t="inlineStr">
         <is>
-          <t>https://specs.optimism.io/experimental/gov-token.html</t>
+          <t>https://optimism.io/blog/op-token-buybacks</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7830,7 @@
       <c r="C96" s="30" t="n"/>
       <c r="D96" s="30" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E96" s="30" t="inlineStr">
